--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.17811864762008</v>
+        <v>6.366444280238263</v>
       </c>
       <c r="D2" t="n">
-        <v>39.31568386576437</v>
+        <v>6.38879862818671</v>
       </c>
       <c r="E2" t="n">
-        <v>16.19152179891136</v>
+        <v>2.631122292323096</v>
       </c>
       <c r="F2" t="n">
-        <v>16.09276417975589</v>
+        <v>2.615074179210332</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.17135200591907</v>
+        <v>5.227844700961849</v>
       </c>
       <c r="D3" t="n">
-        <v>32.41706911975545</v>
+        <v>5.267773731960261</v>
       </c>
       <c r="E3" t="n">
-        <v>16.19152179891136</v>
+        <v>2.631122292323096</v>
       </c>
       <c r="F3" t="n">
-        <v>16.09276417975589</v>
+        <v>2.615074179210332</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.40538815594297</v>
+        <v>6.565875575340733</v>
       </c>
       <c r="D4" t="n">
-        <v>40.27641901925601</v>
+        <v>6.544918090629102</v>
       </c>
       <c r="E4" t="n">
-        <v>16.19152179891136</v>
+        <v>2.631122292323096</v>
       </c>
       <c r="F4" t="n">
-        <v>16.09276417975589</v>
+        <v>2.615074179210332</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.7276910458091</v>
+        <v>8.89324979494398</v>
       </c>
       <c r="D5" t="n">
-        <v>54.54196524937358</v>
+        <v>8.863069353023208</v>
       </c>
       <c r="E5" t="n">
-        <v>16.19152179891136</v>
+        <v>2.631122292323096</v>
       </c>
       <c r="F5" t="n">
-        <v>16.09276417975589</v>
+        <v>2.615074179210332</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.90741973990687</v>
+        <v>2.909955707734867</v>
       </c>
       <c r="D6" t="n">
-        <v>18.10104161348365</v>
+        <v>2.941419262191094</v>
       </c>
       <c r="E6" t="n">
-        <v>16.19152179891136</v>
+        <v>2.631122292323096</v>
       </c>
       <c r="F6" t="n">
-        <v>16.09276417975589</v>
+        <v>2.615074179210332</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.55017486580395</v>
+        <v>7.564403415693143</v>
       </c>
       <c r="D7" t="n">
-        <v>46.34946554733936</v>
+        <v>7.531788151442647</v>
       </c>
       <c r="E7" t="n">
-        <v>16.19152179891136</v>
+        <v>2.631122292323096</v>
       </c>
       <c r="F7" t="n">
-        <v>16.09276417975589</v>
+        <v>2.615074179210332</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.42023433310526</v>
+        <v>4.455788079129605</v>
       </c>
       <c r="D8" t="n">
-        <v>27.17728519667918</v>
+        <v>4.416308844460366</v>
       </c>
       <c r="E8" t="n">
-        <v>16.19152179891136</v>
+        <v>2.631122292323096</v>
       </c>
       <c r="F8" t="n">
-        <v>16.09276417975589</v>
+        <v>2.615074179210332</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.83544958538548</v>
+        <v>4.68576055762514</v>
       </c>
       <c r="D9" t="n">
-        <v>28.77226618973083</v>
+        <v>4.675493255831261</v>
       </c>
       <c r="E9" t="n">
-        <v>16.19152179891136</v>
+        <v>2.631122292323096</v>
       </c>
       <c r="F9" t="n">
-        <v>16.09276417975589</v>
+        <v>2.615074179210332</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.0040190739681</v>
+        <v>8.288153099519816</v>
       </c>
       <c r="D10" t="n">
-        <v>50.74654414483294</v>
+        <v>8.246313423535353</v>
       </c>
       <c r="E10" t="n">
-        <v>16.19152179891136</v>
+        <v>2.631122292323096</v>
       </c>
       <c r="F10" t="n">
-        <v>16.09276417975589</v>
+        <v>2.615074179210332</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.128262684914337</v>
+        <v>0.9958426862985799</v>
       </c>
       <c r="D11" t="n">
-        <v>6.393220258157957</v>
+        <v>1.038898291950668</v>
       </c>
       <c r="E11" t="n">
-        <v>16.19152179891136</v>
+        <v>2.631122292323096</v>
       </c>
       <c r="F11" t="n">
-        <v>16.09276417975589</v>
+        <v>2.615074179210332</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.58715060074004</v>
+        <v>3.507911972620256</v>
       </c>
       <c r="D12" t="n">
-        <v>21.28799349744545</v>
+        <v>3.459298943334886</v>
       </c>
       <c r="E12" t="n">
-        <v>16.19152179891136</v>
+        <v>2.631122292323096</v>
       </c>
       <c r="F12" t="n">
-        <v>16.09276417975589</v>
+        <v>2.615074179210332</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>6.019318771522572</v>
+        <v>0.978139300372418</v>
       </c>
       <c r="D13" t="n">
-        <v>5.828383317892705</v>
+        <v>0.9471122891575645</v>
       </c>
       <c r="E13" t="n">
-        <v>16.19152179891136</v>
+        <v>2.631122292323096</v>
       </c>
       <c r="F13" t="n">
-        <v>16.09276417975589</v>
+        <v>2.615074179210332</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>7.116376704872476</v>
+        <v>1.156411214541777</v>
       </c>
       <c r="D14" t="n">
-        <v>7.419381972506509</v>
+        <v>1.205649570532308</v>
       </c>
       <c r="E14" t="n">
-        <v>16.19152179891136</v>
+        <v>2.631122292323096</v>
       </c>
       <c r="F14" t="n">
-        <v>16.09276417975589</v>
+        <v>2.615074179210332</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
